--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0004.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0004.xlsx
@@ -19424,7 +19424,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>&lt;color=#e0d799&gt;{0}&lt;/color&gt;/{1}</t>
+          <t>{0}/{1}</t>
         </is>
       </c>
     </row>
